--- a/samples/s13_科目余额表.xlsx
+++ b/samples/s13_科目余额表.xlsx
@@ -423,7 +423,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>邯郸市甲辰建材有限公司</v>
+        <v>某市甲辰建材有限公司</v>
       </c>
       <c r="B3">
         <v>20000</v>
@@ -440,7 +440,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>邯郸市丙通物流有限公司</v>
+        <v>某市丙通物流有限公司</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>邯郸市某某商贸有限公司</v>
+        <v>某市某某商贸有限公司</v>
       </c>
       <c r="B5">
         <v>5000</v>
